--- a/output/pdf_financials_xlsx/GDN.xlsx
+++ b/output/pdf_financials_xlsx/GDN.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007804</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004925</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002481</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.1283</v>
+        <v>-0.136104</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.09898700000000001</v>
+        <v>-0.103912</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.255005</v>
+        <v>-0.257486</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.1283</v>
+        <v>-0.136104</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.09898700000000001</v>
+        <v>-0.103912</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.255005</v>
+        <v>-0.257486</v>
       </c>
     </row>
     <row r="30">
@@ -986,7 +986,7 @@
         <v>0.110599</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.010228</v>
       </c>
     </row>
     <row r="35">
@@ -1018,7 +1018,7 @@
         <v>0.110599</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.010228</v>
       </c>
     </row>
     <row r="37">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.149572</v>
+        <v>0.139344</v>
       </c>
     </row>
     <row r="49">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">

--- a/output/pdf_financials_xlsx/GDN.xlsx
+++ b/output/pdf_financials_xlsx/GDN.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.020018</v>
+        <v>0.08176799999999999</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.019307</v>
+        <v>0.083318</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.026639</v>
+        <v>0.133447</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.026407</v>
+        <v>0.088157</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.026457</v>
+        <v>0.09046800000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.039417</v>
+        <v>0.146225</v>
       </c>
     </row>
     <row r="11">
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="36">
@@ -1018,7 +1018,7 @@
         <v>0.110599</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.010228</v>
+        <v>0.140228</v>
       </c>
     </row>
     <row r="37">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.139344</v>
+        <v>0.009344</v>
       </c>
     </row>
     <row r="49">
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>0.068854</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
+        <v>0.083533</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>0.142108</v>
       </c>
     </row>
     <row r="59">
@@ -1421,10 +1421,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.09406200000000001</v>
+        <v>0.010529</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.258261</v>
+        <v>0.116153</v>
       </c>
     </row>
     <row r="62">
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.08977499999999999</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.152775</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>0.056008</v>
       </c>
     </row>
     <row r="67">
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.414426</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>0.414426</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.82687</v>
       </c>
     </row>
     <row r="89">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.10693</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.10693</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.09173000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.031098</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -2796,7 +2796,11 @@
           <t>Marketable securities – Note 5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -2889,7 +2893,11 @@
           <t>Exploration and evaluation assets – Notes 6 and 9</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.068854</v>
       </c>
@@ -2947,7 +2955,11 @@
           <t>Due to related parties – Note 9</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2978,7 +2990,11 @@
           <t>Due to related parties – Note 9</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.08977499999999999</v>
       </c>
@@ -3038,7 +3054,11 @@
           <t>Share capital – Notes 6, 7 and 9</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3067,7 +3087,11 @@
           <t>Contributed surplus – Notes 7 and 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3216,7 +3240,11 @@
           <t>Share capital – Notes 6 and 7</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.414426</v>
       </c>
@@ -3245,7 +3273,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.10693</v>
       </c>
@@ -4382,7 +4414,11 @@
           <t>Share-based payments – Note 7</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.031098</v>
       </c>
@@ -4932,7 +4968,11 @@
           <t>Consulting fees – Note 9</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -5027,7 +5067,11 @@
           <t>Management fees – Note 9</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -5037,7 +5081,7 @@
         <v>0.03</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.001643</v>
+        <v>0.001643</v>
       </c>
     </row>
     <row r="79">
@@ -5153,7 +5197,11 @@
           <t>Travel – Note 9</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -5523,7 +5571,11 @@
           <t>Consulting fees – Note 9</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.03175</v>
       </c>
@@ -5618,7 +5670,11 @@
           <t>Management fees – Note 9</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>0.03</v>
       </c>
